--- a/data/nzd0338/nzd0338.xlsx
+++ b/data/nzd0338/nzd0338.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H682"/>
+  <dimension ref="A1:H685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20898,6 +20898,96 @@
         <v>354.65</v>
       </c>
       <c r="H682" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:01:19+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>372.28</v>
+      </c>
+      <c r="C683" t="n">
+        <v>354.4</v>
+      </c>
+      <c r="D683" t="n">
+        <v>359.35</v>
+      </c>
+      <c r="E683" t="n">
+        <v>351.98</v>
+      </c>
+      <c r="F683" t="n">
+        <v>358.52</v>
+      </c>
+      <c r="G683" t="n">
+        <v>354.95</v>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:07:32+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>371.74</v>
+      </c>
+      <c r="C684" t="n">
+        <v>354.27</v>
+      </c>
+      <c r="D684" t="n">
+        <v>359.24</v>
+      </c>
+      <c r="E684" t="n">
+        <v>352.39</v>
+      </c>
+      <c r="F684" t="n">
+        <v>359.19</v>
+      </c>
+      <c r="G684" t="n">
+        <v>354.97</v>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>371.29</v>
+      </c>
+      <c r="C685" t="n">
+        <v>354.3</v>
+      </c>
+      <c r="D685" t="n">
+        <v>359.26</v>
+      </c>
+      <c r="E685" t="n">
+        <v>352.44</v>
+      </c>
+      <c r="F685" t="n">
+        <v>359.79</v>
+      </c>
+      <c r="G685" t="n">
+        <v>355.32</v>
+      </c>
+      <c r="H685" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20914,7 +21004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B715"/>
+  <dimension ref="A1:B718"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28067,6 +28157,36 @@
       </c>
       <c r="B715" t="n">
         <v>-0.09</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B716" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B717" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B718" t="n">
+        <v>-0.13</v>
       </c>
     </row>
   </sheetData>
@@ -28235,28 +28355,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06160306260445196</v>
+        <v>-0.06212095259474891</v>
       </c>
       <c r="J2" t="n">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="K2" t="n">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02969354183879191</v>
+        <v>0.03044687403331769</v>
       </c>
       <c r="M2" t="n">
-        <v>2.017341269404842</v>
+        <v>2.011186068832266</v>
       </c>
       <c r="N2" t="n">
-        <v>6.759671144447906</v>
+        <v>6.732282681926692</v>
       </c>
       <c r="O2" t="n">
-        <v>2.599936757778524</v>
+        <v>2.594664271524679</v>
       </c>
       <c r="P2" t="n">
-        <v>373.986576850712</v>
+        <v>373.9919703871577</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28313,28 +28433,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1105340210762426</v>
+        <v>0.107740724954227</v>
       </c>
       <c r="J3" t="n">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="K3" t="n">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1200237017135277</v>
+        <v>0.1147390619223811</v>
       </c>
       <c r="M3" t="n">
-        <v>1.747196511976878</v>
+        <v>1.75396218580569</v>
       </c>
       <c r="N3" t="n">
-        <v>4.882811273397534</v>
+        <v>4.906558968933764</v>
       </c>
       <c r="O3" t="n">
-        <v>2.209708413659489</v>
+        <v>2.215075386738285</v>
       </c>
       <c r="P3" t="n">
-        <v>354.6499057878905</v>
+        <v>354.6789819608419</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28391,28 +28511,28 @@
         <v>0.1762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0587968184306308</v>
+        <v>0.05498110232669658</v>
       </c>
       <c r="J4" t="n">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="K4" t="n">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02875638986287843</v>
+        <v>0.0251432548527436</v>
       </c>
       <c r="M4" t="n">
-        <v>1.972701311547105</v>
+        <v>1.983065435387701</v>
       </c>
       <c r="N4" t="n">
-        <v>6.364664368541868</v>
+        <v>6.421011066909189</v>
       </c>
       <c r="O4" t="n">
-        <v>2.522828644308184</v>
+        <v>2.533971402149044</v>
       </c>
       <c r="P4" t="n">
-        <v>362.1484902478379</v>
+        <v>362.1882089400207</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28469,28 +28589,28 @@
         <v>0.1963</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0530051126058645</v>
+        <v>-0.05669917563051281</v>
       </c>
       <c r="J5" t="n">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="K5" t="n">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01620804982193513</v>
+        <v>0.01851912327708405</v>
       </c>
       <c r="M5" t="n">
-        <v>2.508821595534445</v>
+        <v>2.516904606353211</v>
       </c>
       <c r="N5" t="n">
-        <v>9.295699301074794</v>
+        <v>9.33409330506877</v>
       </c>
       <c r="O5" t="n">
-        <v>3.048884927489851</v>
+        <v>3.055174840343637</v>
       </c>
       <c r="P5" t="n">
-        <v>357.9334171404918</v>
+        <v>357.9718680191216</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28547,28 +28667,28 @@
         <v>0.1494</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03503371016418043</v>
+        <v>-0.03703912937741258</v>
       </c>
       <c r="J6" t="n">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="K6" t="n">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005909277472560204</v>
+        <v>0.006648216888837433</v>
       </c>
       <c r="M6" t="n">
-        <v>2.715825690375661</v>
+        <v>2.714963259516804</v>
       </c>
       <c r="N6" t="n">
-        <v>11.25480423238376</v>
+        <v>11.22992007383342</v>
       </c>
       <c r="O6" t="n">
-        <v>3.354818062486215</v>
+        <v>3.351107290707569</v>
       </c>
       <c r="P6" t="n">
-        <v>362.4096052169609</v>
+        <v>362.4304764290782</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28625,28 +28745,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1057340946535974</v>
+        <v>-0.1092818701072221</v>
       </c>
       <c r="J7" t="n">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="K7" t="n">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03911559984528479</v>
+        <v>0.04185498253912334</v>
       </c>
       <c r="M7" t="n">
-        <v>3.178810315042603</v>
+        <v>3.183024040051942</v>
       </c>
       <c r="N7" t="n">
-        <v>14.97012036140287</v>
+        <v>14.97743854689145</v>
       </c>
       <c r="O7" t="n">
-        <v>3.869123978551588</v>
+        <v>3.870069579076253</v>
       </c>
       <c r="P7" t="n">
-        <v>361.9625790920146</v>
+        <v>361.9995074223282</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28684,7 +28804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H682"/>
+  <dimension ref="A1:H685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57331,6 +57451,132 @@
         </is>
       </c>
     </row>
+    <row r="683">
+      <c r="A683" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:01:19+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>-41.06973191633231,174.85343482977927</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>-41.0690342755333,174.8534178946256</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>-41.06841080621536,174.85311404411965</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>-41.06780586549634,174.85272789116422</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>-41.06727602412014,174.85217287787702</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>-41.06672233004927,174.85165882794018</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:07:32+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>-41.06973064607851,174.85344103236184</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>-41.06903394910884,174.8534193801821</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>-41.06841039227404,174.85311523327064</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>-41.067807882517286,174.85272380485256</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>-41.06727959598809,174.85216645264734</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>-41.06672244214577,174.85165864167215</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>-41.06972958753343,174.85344620118047</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>-41.06903402443756,174.85341903736133</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>-41.06841046753611,174.85311501706138</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>-41.067808128495436,174.85272330652185</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>-41.06728279467551,174.85216069870972</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>-41.0667244038346,174.85165538198154</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0338/nzd0338.xlsx
+++ b/data/nzd0338/nzd0338.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H685"/>
+  <dimension ref="A1:H687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20990,6 +20990,66 @@
       <c r="H685" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-01 22:01:18+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>370.96</v>
+      </c>
+      <c r="C686" t="n">
+        <v>354.2</v>
+      </c>
+      <c r="D686" t="n">
+        <v>359.29</v>
+      </c>
+      <c r="E686" t="n">
+        <v>352.54</v>
+      </c>
+      <c r="F686" t="n">
+        <v>359.62</v>
+      </c>
+      <c r="G686" t="n">
+        <v>355.28</v>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:30+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>370.94</v>
+      </c>
+      <c r="C687" t="n">
+        <v>354.3</v>
+      </c>
+      <c r="D687" t="n">
+        <v>359.91</v>
+      </c>
+      <c r="E687" t="n">
+        <v>353.27</v>
+      </c>
+      <c r="F687" t="n">
+        <v>360.49</v>
+      </c>
+      <c r="G687" t="n">
+        <v>357.75</v>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -21004,7 +21064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B718"/>
+  <dimension ref="A1:B720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28187,6 +28247,26 @@
       </c>
       <c r="B718" t="n">
         <v>-0.13</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2025-12-01 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B719" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B720" t="n">
+        <v>0.18</v>
       </c>
     </row>
   </sheetData>
@@ -28355,28 +28435,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06212095259474891</v>
+        <v>-0.06292824811568547</v>
       </c>
       <c r="J2" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="K2" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03044687403331769</v>
+        <v>0.03138135943927545</v>
       </c>
       <c r="M2" t="n">
-        <v>2.011186068832266</v>
+        <v>2.009498938913162</v>
       </c>
       <c r="N2" t="n">
-        <v>6.732282681926692</v>
+        <v>6.718391344174964</v>
       </c>
       <c r="O2" t="n">
-        <v>2.594664271524679</v>
+        <v>2.59198598456376</v>
       </c>
       <c r="P2" t="n">
-        <v>373.9919703871577</v>
+        <v>374.0003862746032</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28433,28 +28513,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.107740724954227</v>
+        <v>0.1058685304465275</v>
       </c>
       <c r="J3" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="K3" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1147390619223811</v>
+        <v>0.1112196191355207</v>
       </c>
       <c r="M3" t="n">
-        <v>1.75396218580569</v>
+        <v>1.758644535608506</v>
       </c>
       <c r="N3" t="n">
-        <v>4.906558968933764</v>
+        <v>4.923112621643309</v>
       </c>
       <c r="O3" t="n">
-        <v>2.215075386738285</v>
+        <v>2.218808829449556</v>
       </c>
       <c r="P3" t="n">
-        <v>354.6789819608419</v>
+        <v>354.6984990317918</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28511,28 +28591,28 @@
         <v>0.1762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05498110232669658</v>
+        <v>0.05267084065674064</v>
       </c>
       <c r="J4" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="K4" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0251432548527436</v>
+        <v>0.02309699077125316</v>
       </c>
       <c r="M4" t="n">
-        <v>1.983065435387701</v>
+        <v>1.988929001864688</v>
       </c>
       <c r="N4" t="n">
-        <v>6.421011066909189</v>
+        <v>6.449551162056877</v>
       </c>
       <c r="O4" t="n">
-        <v>2.533971402149044</v>
+        <v>2.539596653418979</v>
       </c>
       <c r="P4" t="n">
-        <v>362.1882089400207</v>
+        <v>362.2122920907272</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28589,28 +28669,28 @@
         <v>0.1963</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05669917563051281</v>
+        <v>-0.05874518770702785</v>
       </c>
       <c r="J5" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="K5" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01851912327708405</v>
+        <v>0.01989624814293534</v>
       </c>
       <c r="M5" t="n">
-        <v>2.516904606353211</v>
+        <v>2.520249742185799</v>
       </c>
       <c r="N5" t="n">
-        <v>9.33409330506877</v>
+        <v>9.344119851305081</v>
       </c>
       <c r="O5" t="n">
-        <v>3.055174840343637</v>
+        <v>3.056815311939058</v>
       </c>
       <c r="P5" t="n">
-        <v>357.9718680191216</v>
+        <v>357.9931962821189</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28667,28 +28747,28 @@
         <v>0.1494</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03703912937741258</v>
+        <v>-0.03784201093159971</v>
       </c>
       <c r="J6" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="K6" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006648216888837433</v>
+        <v>0.00697670722047572</v>
       </c>
       <c r="M6" t="n">
-        <v>2.714963259516804</v>
+        <v>2.711464370580266</v>
       </c>
       <c r="N6" t="n">
-        <v>11.22992007383342</v>
+        <v>11.20341173203101</v>
       </c>
       <c r="O6" t="n">
-        <v>3.351107290707569</v>
+        <v>3.347149792290601</v>
       </c>
       <c r="P6" t="n">
-        <v>362.4304764290782</v>
+        <v>362.4388451564683</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28745,28 +28825,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1092818701072221</v>
+        <v>-0.1107759121126333</v>
       </c>
       <c r="J7" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="K7" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04185498253912334</v>
+        <v>0.04314766801058167</v>
       </c>
       <c r="M7" t="n">
-        <v>3.183024040051942</v>
+        <v>3.18139134909375</v>
       </c>
       <c r="N7" t="n">
-        <v>14.97743854689145</v>
+        <v>14.9579199970346</v>
       </c>
       <c r="O7" t="n">
-        <v>3.870069579076253</v>
+        <v>3.867547025833636</v>
       </c>
       <c r="P7" t="n">
-        <v>361.9995074223282</v>
+        <v>362.0150792597567</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28804,7 +28884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H685"/>
+  <dimension ref="A1:H687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57577,6 +57657,90 @@
         </is>
       </c>
     </row>
+    <row r="686">
+      <c r="A686" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-01 22:01:18+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>-41.069728811266884,174.85344999164732</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>-41.06903377334182,174.8534201800971</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>-41.06841058042918,174.85311469274745</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>-41.06780862045174,174.8527223098604</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>-41.06728188838077,174.8521623289921</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>-41.0667241796416,174.85165575451762</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:30+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>-41.06972876422043,174.85345022137258</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>-41.06903402443756,174.85341903736133</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>-41.06841291355281,174.8531079902597</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>-41.067812211732495,174.85271503423155</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>-41.067286526477154,174.8521539857818</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>-41.066738023557456,174.85163275040992</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0338/nzd0338.xlsx
+++ b/data/nzd0338/nzd0338.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H687"/>
+  <dimension ref="A1:H689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21050,6 +21050,66 @@
       <c r="H687" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:29+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>369.85</v>
+      </c>
+      <c r="C688" t="n">
+        <v>353.9</v>
+      </c>
+      <c r="D688" t="n">
+        <v>360.09</v>
+      </c>
+      <c r="E688" t="n">
+        <v>353.96</v>
+      </c>
+      <c r="F688" t="n">
+        <v>361.15</v>
+      </c>
+      <c r="G688" t="n">
+        <v>358.31</v>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:07:37+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>369.86</v>
+      </c>
+      <c r="C689" t="n">
+        <v>353.93</v>
+      </c>
+      <c r="D689" t="n">
+        <v>360.02</v>
+      </c>
+      <c r="E689" t="n">
+        <v>353.84</v>
+      </c>
+      <c r="F689" t="n">
+        <v>360.99</v>
+      </c>
+      <c r="G689" t="n">
+        <v>358.32</v>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21064,7 +21124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B720"/>
+  <dimension ref="A1:B722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28267,6 +28327,26 @@
       </c>
       <c r="B720" t="n">
         <v>0.18</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>0.29</v>
       </c>
     </row>
   </sheetData>
@@ -28435,28 +28515,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06292824811568547</v>
+        <v>-0.06434661580876533</v>
       </c>
       <c r="J2" t="n">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="K2" t="n">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03138135943927545</v>
+        <v>0.03287856686717205</v>
       </c>
       <c r="M2" t="n">
-        <v>2.009498938913162</v>
+        <v>2.010943016309924</v>
       </c>
       <c r="N2" t="n">
-        <v>6.718391344174964</v>
+        <v>6.716629988825759</v>
       </c>
       <c r="O2" t="n">
-        <v>2.59198598456376</v>
+        <v>2.591646192832995</v>
       </c>
       <c r="P2" t="n">
-        <v>374.0003862746032</v>
+        <v>374.0152151573841</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28513,28 +28593,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1058685304465275</v>
+        <v>0.1038254145066155</v>
       </c>
       <c r="J3" t="n">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="K3" t="n">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1112196191355207</v>
+        <v>0.1073043579291945</v>
       </c>
       <c r="M3" t="n">
-        <v>1.758644535608506</v>
+        <v>1.764270344699113</v>
       </c>
       <c r="N3" t="n">
-        <v>4.923112621643309</v>
+        <v>4.94567159641691</v>
       </c>
       <c r="O3" t="n">
-        <v>2.218808829449556</v>
+        <v>2.223886597022634</v>
       </c>
       <c r="P3" t="n">
-        <v>354.6984990317918</v>
+        <v>354.7198595643063</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28591,28 +28671,28 @@
         <v>0.1762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05267084065674064</v>
+        <v>0.05064704130944028</v>
       </c>
       <c r="J4" t="n">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="K4" t="n">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02309699077125316</v>
+        <v>0.0214062655804822</v>
       </c>
       <c r="M4" t="n">
-        <v>1.988929001864688</v>
+        <v>1.993519124434812</v>
       </c>
       <c r="N4" t="n">
-        <v>6.449551162056877</v>
+        <v>6.466980545726131</v>
       </c>
       <c r="O4" t="n">
-        <v>2.539596653418979</v>
+        <v>2.543025864148088</v>
       </c>
       <c r="P4" t="n">
-        <v>362.2122920907272</v>
+        <v>362.2334508188607</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28669,28 +28749,28 @@
         <v>0.1963</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05874518770702785</v>
+        <v>-0.06019654167497009</v>
       </c>
       <c r="J5" t="n">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="K5" t="n">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01989624814293534</v>
+        <v>0.02095731710387883</v>
       </c>
       <c r="M5" t="n">
-        <v>2.520249742185799</v>
+        <v>2.520443058603069</v>
       </c>
       <c r="N5" t="n">
-        <v>9.344119851305081</v>
+        <v>9.335571240437314</v>
       </c>
       <c r="O5" t="n">
-        <v>3.056815311939058</v>
+        <v>3.055416704876327</v>
       </c>
       <c r="P5" t="n">
-        <v>357.9931962821189</v>
+        <v>358.00837022589</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28747,28 +28827,28 @@
         <v>0.1494</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03784201093159971</v>
+        <v>-0.0380537337404362</v>
       </c>
       <c r="J6" t="n">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="K6" t="n">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00697670722047572</v>
+        <v>0.007097915233114538</v>
       </c>
       <c r="M6" t="n">
-        <v>2.711464370580266</v>
+        <v>2.704736250652235</v>
       </c>
       <c r="N6" t="n">
-        <v>11.20341173203101</v>
+        <v>11.17125685672743</v>
       </c>
       <c r="O6" t="n">
-        <v>3.347149792290601</v>
+        <v>3.342343019010381</v>
       </c>
       <c r="P6" t="n">
-        <v>362.4388451564683</v>
+        <v>362.4410589255531</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28825,28 +28905,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1107759121126333</v>
+        <v>-0.1112220142746035</v>
       </c>
       <c r="J7" t="n">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="K7" t="n">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04314766801058167</v>
+        <v>0.04373542822483611</v>
       </c>
       <c r="M7" t="n">
-        <v>3.18139134909375</v>
+        <v>3.17441788387376</v>
       </c>
       <c r="N7" t="n">
-        <v>14.9579199970346</v>
+        <v>14.91619554689209</v>
       </c>
       <c r="O7" t="n">
-        <v>3.867547025833636</v>
+        <v>3.862149083980587</v>
       </c>
       <c r="P7" t="n">
-        <v>362.0150792597567</v>
+        <v>362.0197431948059</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28884,7 +28964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H687"/>
+  <dimension ref="A1:H689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57741,6 +57821,90 @@
         </is>
       </c>
     </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:29+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>-41.06972620018764,174.85346274139883</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>-41.069033020054526,174.85342360830427</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>-41.068413590911234,174.85310604437603</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>-41.06781560623034,174.85270815726653</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>-41.06729004503264,174.85214765644903</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>-41.06674116225841,174.85162753490238</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:07:37+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>-41.06972622371087,174.8534626265362</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>-41.06903309538326,174.85342326548357</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>-41.06841332749408,174.85310680110857</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>-41.06781501588291,174.8527093532605</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>-41.067289192049536,174.85214919083282</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>-41.066741218306646,174.8516274417683</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0338/nzd0338.xlsx
+++ b/data/nzd0338/nzd0338.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H689"/>
+  <dimension ref="A1:H691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21110,6 +21110,66 @@
       <c r="H689" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-18 22:01:11+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>371.68</v>
+      </c>
+      <c r="C690" t="n">
+        <v>354.71</v>
+      </c>
+      <c r="D690" t="n">
+        <v>361.18</v>
+      </c>
+      <c r="E690" t="n">
+        <v>355.66</v>
+      </c>
+      <c r="F690" t="n">
+        <v>363.17</v>
+      </c>
+      <c r="G690" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:07:14+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>369.79</v>
+      </c>
+      <c r="C691" t="n">
+        <v>354.49</v>
+      </c>
+      <c r="D691" t="n">
+        <v>361.18</v>
+      </c>
+      <c r="E691" t="n">
+        <v>356.28</v>
+      </c>
+      <c r="F691" t="n">
+        <v>363.84</v>
+      </c>
+      <c r="G691" t="n">
+        <v>360.43</v>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -21124,7 +21184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B722"/>
+  <dimension ref="A1:B724"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28347,6 +28407,26 @@
       </c>
       <c r="B722" t="n">
         <v>0.29</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-01-18 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>-0.16</v>
       </c>
     </row>
   </sheetData>
@@ -28515,28 +28595,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06434661580876533</v>
+        <v>-0.06524870661909701</v>
       </c>
       <c r="J2" t="n">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="K2" t="n">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03287856686717205</v>
+        <v>0.03393252549940362</v>
       </c>
       <c r="M2" t="n">
-        <v>2.010943016309924</v>
+        <v>2.009724846506737</v>
       </c>
       <c r="N2" t="n">
-        <v>6.716629988825759</v>
+        <v>6.706891028238513</v>
       </c>
       <c r="O2" t="n">
-        <v>2.591646192832995</v>
+        <v>2.589766597251288</v>
       </c>
       <c r="P2" t="n">
-        <v>374.0152151573841</v>
+        <v>374.024691732251</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28593,28 +28673,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1038254145066155</v>
+        <v>0.1021884046816139</v>
       </c>
       <c r="J3" t="n">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="K3" t="n">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1073043579291945</v>
+        <v>0.1044340133539275</v>
       </c>
       <c r="M3" t="n">
-        <v>1.764270344699113</v>
+        <v>1.767706421578626</v>
       </c>
       <c r="N3" t="n">
-        <v>4.94567159641691</v>
+        <v>4.95501553110141</v>
       </c>
       <c r="O3" t="n">
-        <v>2.223886597022634</v>
+        <v>2.225986417546479</v>
       </c>
       <c r="P3" t="n">
-        <v>354.7198595643063</v>
+        <v>354.7370431931827</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28671,28 +28751,28 @@
         <v>0.1762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05064704130944028</v>
+        <v>0.04928175640569097</v>
       </c>
       <c r="J4" t="n">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="K4" t="n">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0214062655804822</v>
+        <v>0.02036459323180639</v>
       </c>
       <c r="M4" t="n">
-        <v>1.993519124434812</v>
+        <v>1.994688185101558</v>
       </c>
       <c r="N4" t="n">
-        <v>6.466980545726131</v>
+        <v>6.464683210151228</v>
       </c>
       <c r="O4" t="n">
-        <v>2.543025864148088</v>
+        <v>2.542574130709118</v>
       </c>
       <c r="P4" t="n">
-        <v>362.2334508188607</v>
+        <v>362.2477813699553</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28749,28 +28829,28 @@
         <v>0.1963</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06019654167497009</v>
+        <v>-0.06044985687428698</v>
       </c>
       <c r="J5" t="n">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="K5" t="n">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02095731710387883</v>
+        <v>0.02125814098989043</v>
       </c>
       <c r="M5" t="n">
-        <v>2.520443058603069</v>
+        <v>2.514438137899184</v>
       </c>
       <c r="N5" t="n">
-        <v>9.335571240437314</v>
+        <v>9.309355011381975</v>
       </c>
       <c r="O5" t="n">
-        <v>3.055416704876327</v>
+        <v>3.051123565407008</v>
       </c>
       <c r="P5" t="n">
-        <v>358.00837022589</v>
+        <v>358.0110265354018</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28827,28 +28907,28 @@
         <v>0.1494</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0380537337404362</v>
+        <v>-0.03687308598737708</v>
       </c>
       <c r="J6" t="n">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="K6" t="n">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007097915233114538</v>
+        <v>0.006701191759675318</v>
       </c>
       <c r="M6" t="n">
-        <v>2.704736250652235</v>
+        <v>2.702413870479365</v>
       </c>
       <c r="N6" t="n">
-        <v>11.17125685672743</v>
+        <v>11.15149258321524</v>
       </c>
       <c r="O6" t="n">
-        <v>3.342343019010381</v>
+        <v>3.339385060638447</v>
       </c>
       <c r="P6" t="n">
-        <v>362.4410589255531</v>
+        <v>362.4286635911257</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28905,28 +28985,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1112220142746035</v>
+        <v>-0.1105737190755927</v>
       </c>
       <c r="J7" t="n">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="K7" t="n">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04373542822483611</v>
+        <v>0.04349768700490875</v>
       </c>
       <c r="M7" t="n">
-        <v>3.17441788387376</v>
+        <v>3.168474470070338</v>
       </c>
       <c r="N7" t="n">
-        <v>14.91619554689209</v>
+        <v>14.87681127652025</v>
       </c>
       <c r="O7" t="n">
-        <v>3.862149083980587</v>
+        <v>3.857046963224618</v>
       </c>
       <c r="P7" t="n">
-        <v>362.0197431948059</v>
+        <v>362.0129365627452</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28964,7 +29044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H689"/>
+  <dimension ref="A1:H691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57905,6 +57985,90 @@
         </is>
       </c>
     </row>
+    <row r="690">
+      <c r="A690" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-18 22:01:11+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>-41.06973050493919,174.85344172153768</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>-41.069035053929994,174.8534143521447</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>-41.06841769269197,174.8530942609687</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>-41.06782396948419,174.85269121401637</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>-41.067300813942836,174.85212828485064</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>-41.06675057835992,174.8516118883767</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:07:14+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>-41.06972605904817,174.85346343057458</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>-41.06903450151944,174.8534168661634</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>-41.06841769269197,174.8530942609687</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>-41.06782701961146,174.85268503471227</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>-41.06730438580839,174.8521218596161</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>-41.06675304448141,174.85160779047638</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0338/nzd0338.xlsx
+++ b/data/nzd0338/nzd0338.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H691"/>
+  <dimension ref="A1:H692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21170,6 +21170,36 @@
       <c r="H691" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-27 22:01:11+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>369.43</v>
+      </c>
+      <c r="C692" t="n">
+        <v>356.37</v>
+      </c>
+      <c r="D692" t="n">
+        <v>362.6</v>
+      </c>
+      <c r="E692" t="n">
+        <v>357.38</v>
+      </c>
+      <c r="F692" t="n">
+        <v>362.81</v>
+      </c>
+      <c r="G692" t="n">
+        <v>359.89</v>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21184,7 +21214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B724"/>
+  <dimension ref="A1:B725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28427,6 +28457,16 @@
       </c>
       <c r="B724" t="n">
         <v>-0.16</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-02-27 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
@@ -28595,28 +28635,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06524870661909701</v>
+        <v>-0.06606840030034795</v>
       </c>
       <c r="J2" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="K2" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03393252549940362</v>
+        <v>0.03480683899424819</v>
       </c>
       <c r="M2" t="n">
-        <v>2.009724846506737</v>
+        <v>2.01098219827368</v>
       </c>
       <c r="N2" t="n">
-        <v>6.706891028238513</v>
+        <v>6.709018883182243</v>
       </c>
       <c r="O2" t="n">
-        <v>2.589766597251288</v>
+        <v>2.590177384501348</v>
       </c>
       <c r="P2" t="n">
-        <v>374.024691732251</v>
+        <v>374.0333251635006</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28673,28 +28713,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1021884046816139</v>
+        <v>0.1018794002065246</v>
       </c>
       <c r="J3" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="K3" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1044340133539275</v>
+        <v>0.1041300027804694</v>
       </c>
       <c r="M3" t="n">
-        <v>1.767706421578626</v>
+        <v>1.766748220457101</v>
       </c>
       <c r="N3" t="n">
-        <v>4.95501553110141</v>
+        <v>4.949526466683569</v>
       </c>
       <c r="O3" t="n">
-        <v>2.225986417546479</v>
+        <v>2.22475312488455</v>
       </c>
       <c r="P3" t="n">
-        <v>354.7370431931827</v>
+        <v>354.7402977856634</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28751,28 +28791,28 @@
         <v>0.1762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04928175640569097</v>
+        <v>0.0490091595926396</v>
       </c>
       <c r="J4" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="K4" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02036459323180639</v>
+        <v>0.0202025532682536</v>
       </c>
       <c r="M4" t="n">
-        <v>1.994688185101558</v>
+        <v>1.993182487788614</v>
       </c>
       <c r="N4" t="n">
-        <v>6.464683210151228</v>
+        <v>6.456636443889693</v>
       </c>
       <c r="O4" t="n">
-        <v>2.542574130709118</v>
+        <v>2.540991232548765</v>
       </c>
       <c r="P4" t="n">
-        <v>362.2477813699553</v>
+        <v>362.2506524984002</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28829,28 +28869,28 @@
         <v>0.1963</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06044985687428698</v>
+        <v>-0.06017005695028962</v>
       </c>
       <c r="J5" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="K5" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02125814098989043</v>
+        <v>0.02112776630011515</v>
       </c>
       <c r="M5" t="n">
-        <v>2.514438137899184</v>
+        <v>2.512196428774237</v>
       </c>
       <c r="N5" t="n">
-        <v>9.309355011381975</v>
+        <v>9.297261579079587</v>
       </c>
       <c r="O5" t="n">
-        <v>3.051123565407008</v>
+        <v>3.049141121542194</v>
       </c>
       <c r="P5" t="n">
-        <v>358.0110265354018</v>
+        <v>358.0080795401245</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28907,28 +28947,28 @@
         <v>0.1494</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03687308598737708</v>
+        <v>-0.03648446978721748</v>
       </c>
       <c r="J6" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="K6" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006701191759675318</v>
+        <v>0.006580558314579044</v>
       </c>
       <c r="M6" t="n">
-        <v>2.702413870479365</v>
+        <v>2.700303970042876</v>
       </c>
       <c r="N6" t="n">
-        <v>11.15149258321524</v>
+        <v>11.13801430039819</v>
       </c>
       <c r="O6" t="n">
-        <v>3.339385060638447</v>
+        <v>3.337366371916364</v>
       </c>
       <c r="P6" t="n">
-        <v>362.4286635911257</v>
+        <v>362.4245704874172</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28985,28 +29025,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1105737190755927</v>
+        <v>-0.1103406247884001</v>
       </c>
       <c r="J7" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="K7" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04349768700490875</v>
+        <v>0.04345016076374786</v>
       </c>
       <c r="M7" t="n">
-        <v>3.168474470070338</v>
+        <v>3.165055577811846</v>
       </c>
       <c r="N7" t="n">
-        <v>14.87681127652025</v>
+        <v>14.85623883132223</v>
       </c>
       <c r="O7" t="n">
-        <v>3.857046963224618</v>
+        <v>3.854379175862467</v>
       </c>
       <c r="P7" t="n">
-        <v>362.0129365627452</v>
+        <v>362.0104814950179</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29044,7 +29084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H691"/>
+  <dimension ref="A1:H692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58069,6 +58109,48 @@
         </is>
       </c>
     </row>
+    <row r="692">
+      <c r="A692" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-27 22:01:11+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>-41.06972521221134,174.85346756562885</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>-41.06903922211692,174.85339538272936</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>-41.068423036294504,174.8530789101055</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>-41.0678324311268,174.8526740714294</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>-41.067298894731344,174.85213173721516</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>-41.06675001787774,174.85161281971764</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0338/nzd0338.xlsx
+++ b/data/nzd0338/nzd0338.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H692"/>
+  <dimension ref="A1:H694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21198,6 +21198,66 @@
         <v>359.89</v>
       </c>
       <c r="H692" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:20+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>369.91</v>
+      </c>
+      <c r="C693" t="n">
+        <v>356.7</v>
+      </c>
+      <c r="D693" t="n">
+        <v>363.09</v>
+      </c>
+      <c r="E693" t="n">
+        <v>357.93</v>
+      </c>
+      <c r="F693" t="n">
+        <v>363.19</v>
+      </c>
+      <c r="G693" t="n">
+        <v>360.11</v>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:09+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>369.93</v>
+      </c>
+      <c r="C694" t="n">
+        <v>356.79</v>
+      </c>
+      <c r="D694" t="n">
+        <v>363.42</v>
+      </c>
+      <c r="E694" t="n">
+        <v>358.06</v>
+      </c>
+      <c r="F694" t="n">
+        <v>363.41</v>
+      </c>
+      <c r="G694" t="n">
+        <v>360.19</v>
+      </c>
+      <c r="H694" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21214,7 +21274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B725"/>
+  <dimension ref="A1:B727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28467,6 +28527,26 @@
       </c>
       <c r="B725" t="n">
         <v>0.08</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -28635,28 +28715,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06606840030034795</v>
+        <v>-0.06740929808974022</v>
       </c>
       <c r="J2" t="n">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="K2" t="n">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03480683899424819</v>
+        <v>0.03631871241079299</v>
       </c>
       <c r="M2" t="n">
-        <v>2.01098219827368</v>
+        <v>2.011967181816124</v>
       </c>
       <c r="N2" t="n">
-        <v>6.709018883182243</v>
+        <v>6.705545099576081</v>
       </c>
       <c r="O2" t="n">
-        <v>2.590177384501348</v>
+        <v>2.589506729007685</v>
       </c>
       <c r="P2" t="n">
-        <v>374.0333251635006</v>
+        <v>374.047473443252</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28713,28 +28793,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1018794002065246</v>
+        <v>0.1014781981223332</v>
       </c>
       <c r="J3" t="n">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="K3" t="n">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1041300027804694</v>
+        <v>0.1039522786189108</v>
       </c>
       <c r="M3" t="n">
-        <v>1.766748220457101</v>
+        <v>1.763718761224394</v>
       </c>
       <c r="N3" t="n">
-        <v>4.949526466683569</v>
+        <v>4.936670211319843</v>
       </c>
       <c r="O3" t="n">
-        <v>2.22475312488455</v>
+        <v>2.221861879442519</v>
       </c>
       <c r="P3" t="n">
-        <v>354.7402977856634</v>
+        <v>354.7445307831111</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28791,28 +28871,28 @@
         <v>0.1762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0490091595926396</v>
+        <v>0.04884076498471669</v>
       </c>
       <c r="J4" t="n">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="K4" t="n">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0202025532682536</v>
+        <v>0.02018947577629604</v>
       </c>
       <c r="M4" t="n">
-        <v>1.993182487788614</v>
+        <v>1.988278469161828</v>
       </c>
       <c r="N4" t="n">
-        <v>6.456636443889693</v>
+        <v>6.438333479234941</v>
       </c>
       <c r="O4" t="n">
-        <v>2.540991232548765</v>
+        <v>2.537387136255511</v>
       </c>
       <c r="P4" t="n">
-        <v>362.2506524984002</v>
+        <v>362.2524283403835</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28869,28 +28949,28 @@
         <v>0.1963</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06017005695028962</v>
+        <v>-0.05926823117919106</v>
       </c>
       <c r="J5" t="n">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="K5" t="n">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02112776630011515</v>
+        <v>0.02062284149573967</v>
       </c>
       <c r="M5" t="n">
-        <v>2.512196428774237</v>
+        <v>2.509419091379246</v>
       </c>
       <c r="N5" t="n">
-        <v>9.297261579079587</v>
+        <v>9.277626710994531</v>
       </c>
       <c r="O5" t="n">
-        <v>3.049141121542194</v>
+        <v>3.045919682295403</v>
       </c>
       <c r="P5" t="n">
-        <v>358.0080795401245</v>
+        <v>357.9985636364116</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28947,28 +29027,28 @@
         <v>0.1494</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03648446978721748</v>
+        <v>-0.03543502098813163</v>
       </c>
       <c r="J6" t="n">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="K6" t="n">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006580558314579044</v>
+        <v>0.006243135167536162</v>
       </c>
       <c r="M6" t="n">
-        <v>2.700303970042876</v>
+        <v>2.697360175943427</v>
       </c>
       <c r="N6" t="n">
-        <v>11.13801430039819</v>
+        <v>11.11563525816617</v>
       </c>
       <c r="O6" t="n">
-        <v>3.337366371916364</v>
+        <v>3.334011886326467</v>
       </c>
       <c r="P6" t="n">
-        <v>362.4245704874172</v>
+        <v>362.4134966780347</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29025,28 +29105,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1103406247884001</v>
+        <v>-0.1097302395831357</v>
       </c>
       <c r="J7" t="n">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="K7" t="n">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04345016076374786</v>
+        <v>0.04324106242822301</v>
       </c>
       <c r="M7" t="n">
-        <v>3.165055577811846</v>
+        <v>3.15896815514212</v>
       </c>
       <c r="N7" t="n">
-        <v>14.85623883132223</v>
+        <v>14.81666022463106</v>
       </c>
       <c r="O7" t="n">
-        <v>3.854379175862467</v>
+        <v>3.849241512899789</v>
       </c>
       <c r="P7" t="n">
-        <v>362.0104814950179</v>
+        <v>362.0040408309665</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29084,7 +29164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H692"/>
+  <dimension ref="A1:H694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58151,6 +58231,90 @@
         </is>
       </c>
     </row>
+    <row r="693">
+      <c r="A693" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:20+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>-41.06972634132709,174.8534620522231</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>-41.06904005073203,174.85339161170072</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>-41.06842488021323,174.85307361297603</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>-41.0678351368841,174.85266858978724</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>-41.06730092056569,174.8521280930526</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>-41.066751250938516,174.85161077076754</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:09+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>-41.06972638837357,174.85346182249785</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>-41.069040276717935,174.85339058323834</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>-41.0684261220359,174.85307004552135</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>-41.06783577642668,174.85266729412632</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>-41.0673020934171,174.85212598327416</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>-41.06675169932425,174.85161002569478</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0338/nzd0338.xlsx
+++ b/data/nzd0338/nzd0338.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H694"/>
+  <dimension ref="A1:H698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21258,6 +21258,126 @@
         <v>360.19</v>
       </c>
       <c r="H694" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-23 22:00:47+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>369</v>
+      </c>
+      <c r="C695" t="n">
+        <v>356.3</v>
+      </c>
+      <c r="D695" t="n">
+        <v>363.46</v>
+      </c>
+      <c r="E695" t="n">
+        <v>358.09</v>
+      </c>
+      <c r="F695" t="n">
+        <v>363.55</v>
+      </c>
+      <c r="G695" t="n">
+        <v>360.49</v>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:00:57+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>369.68</v>
+      </c>
+      <c r="C696" t="n">
+        <v>356.44</v>
+      </c>
+      <c r="D696" t="n">
+        <v>363.77</v>
+      </c>
+      <c r="E696" t="n">
+        <v>358.07</v>
+      </c>
+      <c r="F696" t="n">
+        <v>363.62</v>
+      </c>
+      <c r="G696" t="n">
+        <v>360.61</v>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="n">
+        <v>369.25</v>
+      </c>
+      <c r="C697" t="n">
+        <v>356.1</v>
+      </c>
+      <c r="D697" t="n">
+        <v>363.33</v>
+      </c>
+      <c r="E697" t="n">
+        <v>357.6</v>
+      </c>
+      <c r="F697" t="n">
+        <v>363.11</v>
+      </c>
+      <c r="G697" t="n">
+        <v>360.09</v>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B698" t="n">
+        <v>369.73</v>
+      </c>
+      <c r="C698" t="n">
+        <v>356.22</v>
+      </c>
+      <c r="D698" t="n">
+        <v>363.57</v>
+      </c>
+      <c r="E698" t="n">
+        <v>357.83</v>
+      </c>
+      <c r="F698" t="n">
+        <v>363.27</v>
+      </c>
+      <c r="G698" t="n">
+        <v>360.09</v>
+      </c>
+      <c r="H698" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21274,7 +21394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B727"/>
+  <dimension ref="A1:B731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28547,6 +28667,46 @@
       </c>
       <c r="B727" t="n">
         <v>0.3</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-03-23 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>-0.14</v>
       </c>
     </row>
   </sheetData>
@@ -28715,28 +28875,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06740929808974022</v>
+        <v>-0.07059596332115044</v>
       </c>
       <c r="J2" t="n">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="K2" t="n">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03631871241079299</v>
+        <v>0.03990907044482361</v>
       </c>
       <c r="M2" t="n">
-        <v>2.011967181816124</v>
+        <v>2.016711457306193</v>
       </c>
       <c r="N2" t="n">
-        <v>6.705545099576081</v>
+        <v>6.712906854720122</v>
       </c>
       <c r="O2" t="n">
-        <v>2.589506729007685</v>
+        <v>2.590927798052296</v>
       </c>
       <c r="P2" t="n">
-        <v>374.047473443252</v>
+        <v>374.0811926146936</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28793,28 +28953,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1014781981223332</v>
+        <v>0.1001458807249614</v>
       </c>
       <c r="J3" t="n">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="K3" t="n">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1039522786189108</v>
+        <v>0.1025094397740254</v>
       </c>
       <c r="M3" t="n">
-        <v>1.763718761224394</v>
+        <v>1.760464748603474</v>
       </c>
       <c r="N3" t="n">
-        <v>4.936670211319843</v>
+        <v>4.916344859674703</v>
       </c>
       <c r="O3" t="n">
-        <v>2.221861879442519</v>
+        <v>2.217283215936725</v>
       </c>
       <c r="P3" t="n">
-        <v>354.7445307831111</v>
+        <v>354.7586311119626</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28871,28 +29031,28 @@
         <v>0.1762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04884076498471669</v>
+        <v>0.0488118960534184</v>
       </c>
       <c r="J4" t="n">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="K4" t="n">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02018947577629604</v>
+        <v>0.020413607988927</v>
       </c>
       <c r="M4" t="n">
-        <v>1.988278469161828</v>
+        <v>1.97765683310742</v>
       </c>
       <c r="N4" t="n">
-        <v>6.438333479234941</v>
+        <v>6.401539913203597</v>
       </c>
       <c r="O4" t="n">
-        <v>2.537387136255511</v>
+        <v>2.530126461899404</v>
       </c>
       <c r="P4" t="n">
-        <v>362.2524283403835</v>
+        <v>362.252734442288</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28949,28 +29109,28 @@
         <v>0.1963</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05926823117919106</v>
+        <v>-0.05760606650218481</v>
       </c>
       <c r="J5" t="n">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="K5" t="n">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02062284149573967</v>
+        <v>0.0197182991329351</v>
       </c>
       <c r="M5" t="n">
-        <v>2.509419091379246</v>
+        <v>2.503167328159265</v>
       </c>
       <c r="N5" t="n">
-        <v>9.277626710994531</v>
+        <v>9.23693775479466</v>
       </c>
       <c r="O5" t="n">
-        <v>3.045919682295403</v>
+        <v>3.039233086618178</v>
       </c>
       <c r="P5" t="n">
-        <v>357.9985636364116</v>
+        <v>357.9809768297742</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29027,28 +29187,28 @@
         <v>0.1494</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03543502098813163</v>
+        <v>-0.03327711990260166</v>
       </c>
       <c r="J6" t="n">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="K6" t="n">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006243135167536162</v>
+        <v>0.005568221508325033</v>
       </c>
       <c r="M6" t="n">
-        <v>2.697360175943427</v>
+        <v>2.691959152892896</v>
       </c>
       <c r="N6" t="n">
-        <v>11.11563525816617</v>
+        <v>11.07286699147271</v>
       </c>
       <c r="O6" t="n">
-        <v>3.334011886326467</v>
+        <v>3.327591770556105</v>
       </c>
       <c r="P6" t="n">
-        <v>362.4134966780347</v>
+        <v>362.3906640927533</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29105,28 +29265,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1097302395831357</v>
+        <v>-0.1083364794679217</v>
       </c>
       <c r="J7" t="n">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="K7" t="n">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04324106242822301</v>
+        <v>0.04267783101464584</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15896815514212</v>
+        <v>3.147720546735795</v>
       </c>
       <c r="N7" t="n">
-        <v>14.81666022463106</v>
+        <v>14.74060616262368</v>
       </c>
       <c r="O7" t="n">
-        <v>3.849241512899789</v>
+        <v>3.839349705695442</v>
       </c>
       <c r="P7" t="n">
-        <v>362.0040408309665</v>
+        <v>361.9892952694938</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29164,7 +29324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H694"/>
+  <dimension ref="A1:H698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58315,6 +58475,174 @@
         </is>
       </c>
     </row>
+    <row r="695">
+      <c r="A695" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-23 22:00:47+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>-41.06972420071158,174.85347250472137</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>-41.06903904635006,174.8533961826445</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>-41.06842627255985,174.85306961310258</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>-41.06783592401343,174.85266699512763</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>-41.06730283977707,174.85212464068783</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>-41.06675338077069,174.85160723167175</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:00:57+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>-41.069725800292495,174.85346469406338</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>-41.06903939788378,174.8533945828142</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>-41.06842743912043,174.85306626185712</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>-41.067835825622275,174.8526671944601</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>-41.06730321295706,174.85212396939468</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>-41.06675405334926,174.85160611406252</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>-41.06972478879287,174.85346963315598</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>-41.06903854415902,174.85339846811638</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>-41.06842578335699,174.85307101846357</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>-41.06783351342975,174.85267187877258</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>-41.06730049407426,174.85212886024473</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>-41.06675113884208,174.85161095703575</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>-41.06972591790871,174.8534641197503</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>-41.06903884547366,174.85339709683328</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>-41.06842668650071,174.85306842395102</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>-41.06783464492824,174.8526695864495</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>-41.06730134705712,174.85212732586044</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>-41.06675113884208,174.85161095703575</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0338/nzd0338.xlsx
+++ b/data/nzd0338/nzd0338.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H698"/>
+  <dimension ref="A1:H705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21378,6 +21378,216 @@
         <v>360.09</v>
       </c>
       <c r="H698" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 22:00:36+00:00</t>
+        </is>
+      </c>
+      <c r="B699" t="n">
+        <v>370</v>
+      </c>
+      <c r="C699" t="n">
+        <v>356.45</v>
+      </c>
+      <c r="D699" t="n">
+        <v>363.76</v>
+      </c>
+      <c r="E699" t="n">
+        <v>358.23</v>
+      </c>
+      <c r="F699" t="n">
+        <v>363.54</v>
+      </c>
+      <c r="G699" t="n">
+        <v>360.22</v>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:42+00:00</t>
+        </is>
+      </c>
+      <c r="B700" t="n">
+        <v>370.22</v>
+      </c>
+      <c r="C700" t="n">
+        <v>356.35</v>
+      </c>
+      <c r="D700" t="n">
+        <v>363.75</v>
+      </c>
+      <c r="E700" t="n">
+        <v>358.06</v>
+      </c>
+      <c r="F700" t="n">
+        <v>363.39</v>
+      </c>
+      <c r="G700" t="n">
+        <v>359.8</v>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B701" t="n">
+        <v>369.67</v>
+      </c>
+      <c r="C701" t="n">
+        <v>356.11</v>
+      </c>
+      <c r="D701" t="n">
+        <v>363.08</v>
+      </c>
+      <c r="E701" t="n">
+        <v>357.49</v>
+      </c>
+      <c r="F701" t="n">
+        <v>362.43</v>
+      </c>
+      <c r="G701" t="n">
+        <v>359.03</v>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-10 22:00:15+00:00</t>
+        </is>
+      </c>
+      <c r="B702" t="n">
+        <v>369.47</v>
+      </c>
+      <c r="C702" t="n">
+        <v>355.95</v>
+      </c>
+      <c r="D702" t="n">
+        <v>362.96</v>
+      </c>
+      <c r="E702" t="n">
+        <v>357.24</v>
+      </c>
+      <c r="F702" t="n">
+        <v>361.99</v>
+      </c>
+      <c r="G702" t="n">
+        <v>358.77</v>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:06:20+00:00</t>
+        </is>
+      </c>
+      <c r="B703" t="n">
+        <v>370.23</v>
+      </c>
+      <c r="C703" t="n">
+        <v>356.06</v>
+      </c>
+      <c r="D703" t="n">
+        <v>363.37</v>
+      </c>
+      <c r="E703" t="n">
+        <v>357.44</v>
+      </c>
+      <c r="F703" t="n">
+        <v>362.22</v>
+      </c>
+      <c r="G703" t="n">
+        <v>358.73</v>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:25+00:00</t>
+        </is>
+      </c>
+      <c r="B704" t="n">
+        <v>370.37</v>
+      </c>
+      <c r="C704" t="n">
+        <v>356.13</v>
+      </c>
+      <c r="D704" t="n">
+        <v>363.43</v>
+      </c>
+      <c r="E704" t="n">
+        <v>357.45</v>
+      </c>
+      <c r="F704" t="n">
+        <v>362</v>
+      </c>
+      <c r="G704" t="n">
+        <v>358.75</v>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:32+00:00</t>
+        </is>
+      </c>
+      <c r="B705" t="n">
+        <v>370.24</v>
+      </c>
+      <c r="C705" t="n">
+        <v>355.99</v>
+      </c>
+      <c r="D705" t="n">
+        <v>363</v>
+      </c>
+      <c r="E705" t="n">
+        <v>356.83</v>
+      </c>
+      <c r="F705" t="n">
+        <v>361.16</v>
+      </c>
+      <c r="G705" t="n">
+        <v>358.28</v>
+      </c>
+      <c r="H705" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21394,7 +21604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B731"/>
+  <dimension ref="A1:B738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28707,6 +28917,76 @@
       </c>
       <c r="B731" t="n">
         <v>-0.14</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-04-24 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-05-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>-0.16</v>
       </c>
     </row>
   </sheetData>
@@ -28875,28 +29155,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07059596332115044</v>
+        <v>-0.07475560524251375</v>
       </c>
       <c r="J2" t="n">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="K2" t="n">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03990907044482361</v>
+        <v>0.04515896309664169</v>
       </c>
       <c r="M2" t="n">
-        <v>2.016711457306193</v>
+        <v>2.018208427356501</v>
       </c>
       <c r="N2" t="n">
-        <v>6.712906854720122</v>
+        <v>6.69227957410632</v>
       </c>
       <c r="O2" t="n">
-        <v>2.590927798052296</v>
+        <v>2.586944060876911</v>
       </c>
       <c r="P2" t="n">
-        <v>374.0811926146936</v>
+        <v>374.1253833258224</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28953,28 +29233,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1001458807249614</v>
+        <v>0.09766759827526515</v>
       </c>
       <c r="J3" t="n">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="K3" t="n">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1025094397740254</v>
+        <v>0.09960443546501618</v>
       </c>
       <c r="M3" t="n">
-        <v>1.760464748603474</v>
+        <v>1.755600545993931</v>
       </c>
       <c r="N3" t="n">
-        <v>4.916344859674703</v>
+        <v>4.883769095268577</v>
       </c>
       <c r="O3" t="n">
-        <v>2.217283215936725</v>
+        <v>2.209925133408047</v>
       </c>
       <c r="P3" t="n">
-        <v>354.7586311119626</v>
+        <v>354.7849644284227</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29031,28 +29311,28 @@
         <v>0.1762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0488118960534184</v>
+        <v>0.04838416405044715</v>
       </c>
       <c r="J4" t="n">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="K4" t="n">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="L4" t="n">
-        <v>0.020413607988927</v>
+        <v>0.02048668532523512</v>
       </c>
       <c r="M4" t="n">
-        <v>1.97765683310742</v>
+        <v>1.961306092100293</v>
       </c>
       <c r="N4" t="n">
-        <v>6.401539913203597</v>
+        <v>6.339347638423207</v>
       </c>
       <c r="O4" t="n">
-        <v>2.530126461899404</v>
+        <v>2.517806116130312</v>
       </c>
       <c r="P4" t="n">
-        <v>362.252734442288</v>
+        <v>362.2572837912547</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29109,28 +29389,28 @@
         <v>0.1963</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05760606650218481</v>
+        <v>-0.05550616610188668</v>
       </c>
       <c r="J5" t="n">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="K5" t="n">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0197182991329351</v>
+        <v>0.01869644980167917</v>
       </c>
       <c r="M5" t="n">
-        <v>2.503167328159265</v>
+        <v>2.488452062759688</v>
       </c>
       <c r="N5" t="n">
-        <v>9.23693775479466</v>
+        <v>9.158537362190019</v>
       </c>
       <c r="O5" t="n">
-        <v>3.039233086618178</v>
+        <v>3.026307545870052</v>
       </c>
       <c r="P5" t="n">
-        <v>357.9809768297742</v>
+        <v>357.9586765998645</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29187,28 +29467,28 @@
         <v>0.1494</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03327711990260166</v>
+        <v>-0.03157130937391577</v>
       </c>
       <c r="J6" t="n">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="K6" t="n">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005568221508325033</v>
+        <v>0.00511681679257403</v>
       </c>
       <c r="M6" t="n">
-        <v>2.691959152892896</v>
+        <v>2.674148554761355</v>
       </c>
       <c r="N6" t="n">
-        <v>11.07286699147271</v>
+        <v>10.97632222489776</v>
       </c>
       <c r="O6" t="n">
-        <v>3.327591770556105</v>
+        <v>3.313053308490185</v>
       </c>
       <c r="P6" t="n">
-        <v>362.3906640927533</v>
+        <v>362.3725586273752</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29265,28 +29545,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1083364794679217</v>
+        <v>-0.1083577720852966</v>
       </c>
       <c r="J7" t="n">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="K7" t="n">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04267783101464584</v>
+        <v>0.04356932369753719</v>
       </c>
       <c r="M7" t="n">
-        <v>3.147720546735795</v>
+        <v>3.121703170102611</v>
       </c>
       <c r="N7" t="n">
-        <v>14.74060616262368</v>
+        <v>14.59796270634739</v>
       </c>
       <c r="O7" t="n">
-        <v>3.839349705695442</v>
+        <v>3.820728033549024</v>
       </c>
       <c r="P7" t="n">
-        <v>361.9892952694938</v>
+        <v>361.9895360058628</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29324,7 +29604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H698"/>
+  <dimension ref="A1:H705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58643,6 +58923,300 @@
         </is>
       </c>
     </row>
+    <row r="699">
+      <c r="A699" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 22:00:36+00:00</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>-41.06972655303627,174.8534610184595</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>-41.06903942299332,174.8533944685406</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>-41.06842740148945,174.85306636996185</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>-41.067836612751606,174.85266559980047</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>-41.067302786465646,174.85212473658686</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>-41.06675186746889,174.8516097462925</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:42+00:00</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>-41.069727070547536,174.85345849148177</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>-41.06903917189783,174.85339561127657</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>-41.06842736385846,174.85306647806652</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>-41.06783577642668,174.85266729412632</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>-41.067301986794256,174.85212617507221</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>-41.06674951344378,174.85161365792447</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>-41.06972577676923,174.85346480892602</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>-41.069038569268564,174.85339835384278</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>-41.068424842582225,174.85307372108073</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>-41.067832972278275,174.852672975101</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>-41.067296868896904,174.8521353813775</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>-41.06674519773074,174.85162082924907</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-10 22:00:15+00:00</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>-41.06972530630433,174.85346710617839</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>-41.06903816751569,174.8534001822202</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>-41.06842439101032,174.85307501833694</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>-41.06783174238854,174.8526754667564</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>-41.067294523193695,174.85213960093364</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>-41.06674374047689,174.8516232507351</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:06:20+00:00</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>-41.06972709407078,174.85345837661916</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>-41.06903844372079,174.85339892521074</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>-41.06842593388096,174.8530705860448</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>-41.06783272630034,174.85267347343208</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>-41.067295749356745,174.85213739525662</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>-41.06674351628399,174.85162362327137</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:25+00:00</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>-41.06972742339611,174.8534567685424</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>-41.06903861948768,174.85339812529557</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>-41.06842615966688,174.85306993741668</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>-41.06783277549593,174.85267337376587</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>-41.067294576505134,174.85213950503464</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>-41.06674362838042,174.8516234370032</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:32+00:00</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>-41.06972711759402,174.85345826175654</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>-41.069038267953914,174.85339972512585</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>-41.068424541534284,174.85307458591822</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>-41.06782972536926,174.85267955307106</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>-41.067290098344095,174.85214756055004</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>-41.06674099411372,174.85162781430458</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0338/nzd0338.xlsx
+++ b/data/nzd0338/nzd0338.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H705"/>
+  <dimension ref="A1:H706"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21590,6 +21590,36 @@
       <c r="H705" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-11 22:00:09+00:00</t>
+        </is>
+      </c>
+      <c r="B706" t="n">
+        <v>370.84</v>
+      </c>
+      <c r="C706" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="D706" t="n">
+        <v>363.13</v>
+      </c>
+      <c r="E706" t="n">
+        <v>356.8</v>
+      </c>
+      <c r="F706" t="n">
+        <v>361.21</v>
+      </c>
+      <c r="G706" t="n">
+        <v>358.18</v>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -21604,7 +21634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B738"/>
+  <dimension ref="A1:B739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28987,6 +29017,16 @@
       </c>
       <c r="B738" t="n">
         <v>-0.16</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-06-11 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -29155,28 +29195,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07475560524251375</v>
+        <v>-0.07510796332082577</v>
       </c>
       <c r="J2" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K2" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04515896309664169</v>
+        <v>0.04568373183066399</v>
       </c>
       <c r="M2" t="n">
-        <v>2.018208427356501</v>
+        <v>2.017175167638159</v>
       </c>
       <c r="N2" t="n">
-        <v>6.69227957410632</v>
+        <v>6.685097221015173</v>
       </c>
       <c r="O2" t="n">
-        <v>2.586944060876911</v>
+        <v>2.585555495636319</v>
       </c>
       <c r="P2" t="n">
-        <v>374.1253833258224</v>
+        <v>374.1291410174591</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29233,28 +29273,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09766759827526515</v>
+        <v>0.09733046156343179</v>
       </c>
       <c r="J3" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K3" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09960443546501618</v>
+        <v>0.09921899478357099</v>
       </c>
       <c r="M3" t="n">
-        <v>1.755600545993931</v>
+        <v>1.754816652512725</v>
       </c>
       <c r="N3" t="n">
-        <v>4.883769095268577</v>
+        <v>4.878956718125734</v>
       </c>
       <c r="O3" t="n">
-        <v>2.209925133408047</v>
+        <v>2.20883605505835</v>
       </c>
       <c r="P3" t="n">
-        <v>354.7849644284227</v>
+        <v>354.7885597931395</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29311,28 +29351,28 @@
         <v>0.1762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04838416405044715</v>
+        <v>0.04826588209237682</v>
       </c>
       <c r="J4" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K4" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02048668532523512</v>
+        <v>0.02044874656864004</v>
       </c>
       <c r="M4" t="n">
-        <v>1.961306092100293</v>
+        <v>1.95911955103993</v>
       </c>
       <c r="N4" t="n">
-        <v>6.339347638423207</v>
+        <v>6.330615987042981</v>
       </c>
       <c r="O4" t="n">
-        <v>2.517806116130312</v>
+        <v>2.516071538538398</v>
       </c>
       <c r="P4" t="n">
-        <v>362.2572837912547</v>
+        <v>362.2585451987602</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29389,28 +29429,28 @@
         <v>0.1963</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05550616610188668</v>
+        <v>-0.05541480047336277</v>
       </c>
       <c r="J5" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K5" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01869644980167917</v>
+        <v>0.01869153870290663</v>
       </c>
       <c r="M5" t="n">
-        <v>2.488452062759688</v>
+        <v>2.485361618332426</v>
       </c>
       <c r="N5" t="n">
-        <v>9.158537362190019</v>
+        <v>9.145701858826429</v>
       </c>
       <c r="O5" t="n">
-        <v>3.026307545870052</v>
+        <v>3.02418614817713</v>
       </c>
       <c r="P5" t="n">
-        <v>357.9586765998645</v>
+        <v>357.9577022391805</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29467,28 +29507,28 @@
         <v>0.1494</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03157130937391577</v>
+        <v>-0.03165879555137384</v>
       </c>
       <c r="J6" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K6" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00511681679257403</v>
+        <v>0.005160606207674778</v>
       </c>
       <c r="M6" t="n">
-        <v>2.674148554761355</v>
+        <v>2.670846645291238</v>
       </c>
       <c r="N6" t="n">
-        <v>10.97632222489776</v>
+        <v>10.96089539250486</v>
       </c>
       <c r="O6" t="n">
-        <v>3.313053308490185</v>
+        <v>3.310724300286096</v>
       </c>
       <c r="P6" t="n">
-        <v>362.3725586273752</v>
+        <v>362.3734916159955</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29545,28 +29585,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1083577720852966</v>
+        <v>-0.1086074697120435</v>
       </c>
       <c r="J7" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K7" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04356932369753719</v>
+        <v>0.04388577954926509</v>
       </c>
       <c r="M7" t="n">
-        <v>3.121703170102611</v>
+        <v>3.118578744004892</v>
       </c>
       <c r="N7" t="n">
-        <v>14.59796270634739</v>
+        <v>14.57841653616122</v>
       </c>
       <c r="O7" t="n">
-        <v>3.820728033549024</v>
+        <v>3.818169264996147</v>
       </c>
       <c r="P7" t="n">
-        <v>361.9895360058628</v>
+        <v>361.9921988841717</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29604,7 +29644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H705"/>
+  <dimension ref="A1:H706"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59217,6 +59257,48 @@
         </is>
       </c>
     </row>
+    <row r="706">
+      <c r="A706" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-11 22:00:09+00:00</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>-41.069728528988115,174.85345136999888</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>-41.06903874503545,174.85339755392764</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>-41.06842503073719,174.85307318055732</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>-41.067829577782476,174.85267985206968</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>-41.06729036490132,174.8521470810551</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>-41.06674043363141,174.85162874564523</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
